--- a/proj/fp-groups.xlsx
+++ b/proj/fp-groups.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10404"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/abmosca/Documents/Smith/teaching/SDS-CSC235/SDS-CSC235/proj/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC235/SDS-CSC235/proj/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8710B1C-E115-9F4D-8739-92F60E346217}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7957DA99-1F7E-0146-B0E3-FED7F7368AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="760" yWindow="600" windowWidth="28040" windowHeight="15680" xr2:uid="{71E62EC8-1AF9-0848-97F7-357574D51BB9}"/>
+    <workbookView xWindow="23600" yWindow="920" windowWidth="28040" windowHeight="15680" xr2:uid="{71E62EC8-1AF9-0848-97F7-357574D51BB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -168,17 +168,17 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color rgb="FFFF0000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <b/>
       <sz val="12"/>
       <color theme="0"/>
       <name val="Aptos Narrow"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="5"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -232,9 +232,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="16">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -245,13 +245,16 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -264,7 +267,7 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -623,80 +626,80 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="14" t="s">
+      <c r="A2" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="10" t="s">
+      <c r="B2" s="7" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="D2" s="9"/>
+      <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="14"/>
-      <c r="B3" s="10" t="s">
+      <c r="A3" s="15"/>
+      <c r="B3" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="16" t="s">
         <v>33</v>
       </c>
-      <c r="D3" s="9"/>
+      <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="14"/>
-      <c r="B4" s="10" t="s">
+      <c r="A4" s="15"/>
+      <c r="B4" s="7" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="16" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" s="7"/>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A5" s="15"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D5" s="7"/>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A6" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="B6" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="C6" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="D6" s="3"/>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A7" s="12"/>
+      <c r="B7" s="8" t="s">
+        <v>9</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D7" s="3"/>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
+      <c r="A8" s="12"/>
+      <c r="B8" s="8" t="s">
+        <v>23</v>
+      </c>
+      <c r="C8" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="D4" s="9"/>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="14"/>
-      <c r="B5" s="10"/>
-      <c r="C5" s="10" t="s">
-        <v>38</v>
-      </c>
-      <c r="D5" s="9"/>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="11" t="s">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="C6" s="8" t="s">
-        <v>35</v>
-      </c>
-      <c r="D6" s="3"/>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="11"/>
-      <c r="B7" s="3" t="s">
-        <v>9</v>
-      </c>
-      <c r="C7" s="8" t="s">
-        <v>36</v>
-      </c>
-      <c r="D7" s="3"/>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="11"/>
-      <c r="B8" s="3" t="s">
-        <v>23</v>
-      </c>
-      <c r="C8" s="8" t="s">
-        <v>37</v>
-      </c>
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="11"/>
-      <c r="B9" s="3" t="s">
+      <c r="A9" s="12"/>
+      <c r="B9" s="8" t="s">
         <v>25</v>
       </c>
       <c r="C9" s="3"/>
@@ -704,50 +707,50 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A10" s="2"/>
-      <c r="B10" s="3" t="s">
+      <c r="B10" s="8" t="s">
         <v>26</v>
       </c>
       <c r="C10" s="3"/>
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="12" t="s">
+      <c r="A11" s="13" t="s">
         <v>5</v>
       </c>
-      <c r="B11" s="5" t="s">
+      <c r="B11" s="9" t="s">
         <v>16</v>
       </c>
-      <c r="C11" s="5" t="s">
+      <c r="C11" s="9" t="s">
         <v>10</v>
       </c>
       <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="12"/>
-      <c r="B12" s="5" t="s">
+      <c r="A12" s="13"/>
+      <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="5" t="s">
+      <c r="C12" s="9" t="s">
         <v>17</v>
       </c>
       <c r="D12" s="5"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="12"/>
-      <c r="B13" s="5" t="s">
+      <c r="A13" s="13"/>
+      <c r="B13" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="5" t="s">
+      <c r="C13" s="9" t="s">
         <v>18</v>
       </c>
       <c r="D13" s="5"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="12"/>
-      <c r="B14" s="5" t="s">
+      <c r="A14" s="13"/>
+      <c r="B14" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="C14" s="5" t="s">
+      <c r="C14" s="9" t="s">
         <v>19</v>
       </c>
       <c r="D14" s="5"/>
@@ -755,50 +758,50 @@
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="5" t="s">
+      <c r="C15" s="9" t="s">
         <v>21</v>
       </c>
       <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="13" t="s">
+      <c r="A16" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="6" t="s">
+      <c r="B16" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C16" s="7" t="s">
+      <c r="C16" s="11" t="s">
         <v>22</v>
       </c>
-      <c r="D16" s="7"/>
+      <c r="D16" s="6"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="13"/>
-      <c r="B17" s="6" t="s">
+      <c r="A17" s="14"/>
+      <c r="B17" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="C17" s="7" t="s">
+      <c r="C17" s="11" t="s">
         <v>24</v>
       </c>
-      <c r="D17" s="7"/>
+      <c r="D17" s="6"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="13"/>
-      <c r="B18" s="6" t="s">
+      <c r="A18" s="14"/>
+      <c r="B18" s="10" t="s">
         <v>15</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="11" t="s">
         <v>27</v>
       </c>
-      <c r="D18" s="7"/>
+      <c r="D18" s="6"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="13"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="15" t="s">
+      <c r="A19" s="14"/>
+      <c r="B19" s="11"/>
+      <c r="C19" s="11" t="s">
         <v>31</v>
       </c>
-      <c r="D19" s="7"/>
+      <c r="D19" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/proj/fp-groups.xlsx
+++ b/proj/fp-groups.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC235/SDS-CSC235/proj/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7957DA99-1F7E-0146-B0E3-FED7F7368AC7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80AD71A2-8258-764A-9ED0-F1B65BD3CB2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="23600" yWindow="920" windowWidth="28040" windowHeight="15680" xr2:uid="{71E62EC8-1AF9-0848-97F7-357574D51BB9}"/>
+    <workbookView xWindow="16760" yWindow="920" windowWidth="28040" windowHeight="15680" xr2:uid="{71E62EC8-1AF9-0848-97F7-357574D51BB9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -255,6 +255,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -267,7 +268,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -626,79 +626,79 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="C2" s="16" t="s">
+      <c r="C2" s="12" t="s">
         <v>32</v>
       </c>
       <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="15"/>
-      <c r="B3" s="7" t="s">
+      <c r="A3" s="16"/>
+      <c r="B3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="C3" s="16" t="s">
+      <c r="C3" s="12" t="s">
         <v>33</v>
       </c>
       <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="15"/>
-      <c r="B4" s="7" t="s">
+      <c r="A4" s="16"/>
+      <c r="B4" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="C4" s="16" t="s">
+      <c r="C4" s="12" t="s">
         <v>37</v>
       </c>
       <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="15"/>
+      <c r="A5" s="16"/>
       <c r="B5" s="7"/>
-      <c r="C5" s="16" t="s">
+      <c r="C5" s="12" t="s">
         <v>38</v>
       </c>
       <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="12" t="s">
+      <c r="A6" s="13" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="8" t="s">
         <v>8</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C6" s="8" t="s">
         <v>35</v>
       </c>
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="12"/>
+      <c r="A7" s="13"/>
       <c r="B7" s="8" t="s">
         <v>9</v>
       </c>
-      <c r="C7" s="3" t="s">
+      <c r="C7" s="8" t="s">
         <v>36</v>
       </c>
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="12"/>
+      <c r="A8" s="13"/>
       <c r="B8" s="8" t="s">
         <v>23</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="C8" s="8" t="s">
         <v>34</v>
       </c>
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="12"/>
+      <c r="A9" s="13"/>
       <c r="B9" s="8" t="s">
         <v>25</v>
       </c>
@@ -714,7 +714,7 @@
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="13" t="s">
+      <c r="A11" s="14" t="s">
         <v>5</v>
       </c>
       <c r="B11" s="9" t="s">
@@ -726,7 +726,7 @@
       <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="13"/>
+      <c r="A12" s="14"/>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
@@ -736,7 +736,7 @@
       <c r="D12" s="5"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="13"/>
+      <c r="A13" s="14"/>
       <c r="B13" s="9" t="s">
         <v>12</v>
       </c>
@@ -746,7 +746,7 @@
       <c r="D13" s="5"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="13"/>
+      <c r="A14" s="14"/>
       <c r="B14" s="9" t="s">
         <v>20</v>
       </c>
@@ -764,7 +764,7 @@
       <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="14" t="s">
+      <c r="A16" s="15" t="s">
         <v>6</v>
       </c>
       <c r="B16" s="10" t="s">
@@ -776,7 +776,7 @@
       <c r="D16" s="6"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="14"/>
+      <c r="A17" s="15"/>
       <c r="B17" s="10" t="s">
         <v>14</v>
       </c>
@@ -786,7 +786,7 @@
       <c r="D17" s="6"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="14"/>
+      <c r="A18" s="15"/>
       <c r="B18" s="10" t="s">
         <v>15</v>
       </c>
@@ -796,7 +796,7 @@
       <c r="D18" s="6"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="14"/>
+      <c r="A19" s="15"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11" t="s">
         <v>31</v>

--- a/proj/fp-groups.xlsx
+++ b/proj/fp-groups.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/amosca/Documents/Smith/teaching/SDS-CSC235/SDS-CSC235/proj/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80AD71A2-8258-764A-9ED0-F1B65BD3CB2D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBB1068C-2968-3644-B95D-E0A66DF631AB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="16760" yWindow="920" windowWidth="28040" windowHeight="15680" xr2:uid="{71E62EC8-1AF9-0848-97F7-357574D51BB9}"/>
   </bookViews>
@@ -159,7 +159,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -177,6 +177,13 @@
     <font>
       <sz val="12"/>
       <color theme="5"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFC00000"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -232,7 +239,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -256,6 +263,12 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -626,7 +639,7 @@
       </c>
     </row>
     <row r="2" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A2" s="16" t="s">
+      <c r="A2" s="18" t="s">
         <v>3</v>
       </c>
       <c r="B2" s="12" t="s">
@@ -638,7 +651,7 @@
       <c r="D2" s="7"/>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A3" s="16"/>
+      <c r="A3" s="18"/>
       <c r="B3" s="12" t="s">
         <v>29</v>
       </c>
@@ -648,7 +661,7 @@
       <c r="D3" s="7"/>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A4" s="16"/>
+      <c r="A4" s="18"/>
       <c r="B4" s="12" t="s">
         <v>30</v>
       </c>
@@ -658,7 +671,7 @@
       <c r="D4" s="7"/>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A5" s="16"/>
+      <c r="A5" s="18"/>
       <c r="B5" s="7"/>
       <c r="C5" s="12" t="s">
         <v>38</v>
@@ -666,7 +679,7 @@
       <c r="D5" s="7"/>
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A6" s="13" t="s">
+      <c r="A6" s="15" t="s">
         <v>4</v>
       </c>
       <c r="B6" s="8" t="s">
@@ -678,7 +691,7 @@
       <c r="D6" s="3"/>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A7" s="13"/>
+      <c r="A7" s="15"/>
       <c r="B7" s="8" t="s">
         <v>9</v>
       </c>
@@ -688,7 +701,7 @@
       <c r="D7" s="3"/>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A8" s="13"/>
+      <c r="A8" s="15"/>
       <c r="B8" s="8" t="s">
         <v>23</v>
       </c>
@@ -698,7 +711,7 @@
       <c r="D8" s="3"/>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A9" s="13"/>
+      <c r="A9" s="15"/>
       <c r="B9" s="8" t="s">
         <v>25</v>
       </c>
@@ -714,7 +727,7 @@
       <c r="D10" s="3"/>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A11" s="14" t="s">
+      <c r="A11" s="16" t="s">
         <v>5</v>
       </c>
       <c r="B11" s="9" t="s">
@@ -726,27 +739,27 @@
       <c r="D11" s="5"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A12" s="14"/>
+      <c r="A12" s="16"/>
       <c r="B12" s="9" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="9" t="s">
+      <c r="C12" s="13" t="s">
         <v>17</v>
       </c>
       <c r="D12" s="5"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A13" s="14"/>
+      <c r="A13" s="16"/>
       <c r="B13" s="9" t="s">
         <v>12</v>
       </c>
-      <c r="C13" s="9" t="s">
+      <c r="C13" s="13" t="s">
         <v>18</v>
       </c>
       <c r="D13" s="5"/>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A14" s="14"/>
+      <c r="A14" s="16"/>
       <c r="B14" s="9" t="s">
         <v>20</v>
       </c>
@@ -758,16 +771,16 @@
     <row r="15" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A15" s="4"/>
       <c r="B15" s="5"/>
-      <c r="C15" s="9" t="s">
+      <c r="C15" s="13" t="s">
         <v>21</v>
       </c>
       <c r="D15" s="5"/>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A16" s="15" t="s">
+      <c r="A16" s="17" t="s">
         <v>6</v>
       </c>
-      <c r="B16" s="10" t="s">
+      <c r="B16" s="14" t="s">
         <v>13</v>
       </c>
       <c r="C16" s="11" t="s">
@@ -776,7 +789,7 @@
       <c r="D16" s="6"/>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A17" s="15"/>
+      <c r="A17" s="17"/>
       <c r="B17" s="10" t="s">
         <v>14</v>
       </c>
@@ -786,7 +799,7 @@
       <c r="D17" s="6"/>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A18" s="15"/>
+      <c r="A18" s="17"/>
       <c r="B18" s="10" t="s">
         <v>15</v>
       </c>
@@ -796,7 +809,7 @@
       <c r="D18" s="6"/>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.2">
-      <c r="A19" s="15"/>
+      <c r="A19" s="17"/>
       <c r="B19" s="11"/>
       <c r="C19" s="11" t="s">
         <v>31</v>
